--- a/docs/sales/services/national-shared-talent-src/Shared-National-Talent-Pricing-INTERNAL.xlsx
+++ b/docs/sales/services/national-shared-talent-src/Shared-National-Talent-Pricing-INTERNAL.xlsx
@@ -702,8 +702,9 @@
           <t>Hours in a full-time month</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
-        <v>176</v>
+      <c r="B6" s="8">
+        <f>5*8*52/12</f>
+        <v/>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -712,7 +713,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>8 hours × 22 days — assumption to confirm</t>
+          <t>5 days × 8 hours × 52 ÷ 12 = 173.33 — owner decision</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1974,7 @@
       </c>
       <c r="G3" s="37" t="inlineStr">
         <is>
-          <t>Full-time price (176 h at 100%)</t>
+          <t>Full-time price (173.33 h at 100%)</t>
         </is>
       </c>
       <c r="H3" s="37" t="inlineStr">
